--- a/artfynd/A 19016-2023 artfynd.xlsx
+++ b/artfynd/A 19016-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19016-2023 artfynd.xlsx
+++ b/artfynd/A 19016-2023 artfynd.xlsx
@@ -1615,7 +1615,7 @@
         <v>108911059</v>
       </c>
       <c r="B10" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629982.4464877233</v>
+        <v>629982</v>
       </c>
       <c r="R10" t="n">
-        <v>6894093.096055195</v>
+        <v>6894093</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,19 +1685,9 @@
           <t>2023-05-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
